--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.30-8.13-14-business-continuity-dr/WKBK/90_workbooks/ISMS-IMP-A.5.30.S3_RPO_RTO_Compliance_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.30-8.13-14-business-continuity-dr/WKBK/90_workbooks/ISMS-IMP-A.5.30.S3_RPO_RTO_Compliance_20260208.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
